--- a/output/pdf_financials_xlsx/BLN.xlsx
+++ b/output/pdf_financials_xlsx/BLN.xlsx
@@ -823,37 +823,37 @@
         <v>6.387497</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.892218</v>
+        <v>7.581439</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5.756649</v>
+        <v>10.573465</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9.030196999999999</v>
+        <v>13.793352</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.574184</v>
+        <v>16.90274</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>19.430341</v>
+        <v>26.227535</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>28.431005</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>59.684</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>85.758</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>77.232</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>84.89400000000001</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>101.129</v>
       </c>
     </row>
     <row r="11">
@@ -869,37 +869,37 @@
         <v>-4.584398</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.486832</v>
+        <v>-4.176053</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.908332</v>
+        <v>-6.725148</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-3.908466</v>
+        <v>-8.671621</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-3.843069</v>
+        <v>-9.171625000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-3.928329</v>
+        <v>-10.725523</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>20.188062</v>
+        <v>-8.242943</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>26.394</v>
+        <v>-33.29</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>32.239</v>
+        <v>-53.519</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>52.781</v>
+        <v>-24.451</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>74.247</v>
+        <v>-10.647</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>95.33199999999999</v>
+        <v>-5.797</v>
       </c>
     </row>
     <row r="12">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.078819</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.040717</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.586293</v>
+        <v>-3.665112</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.543681</v>
+        <v>-4.584398</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.151881</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.586293</v>
+        <v>-3.665112</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.543681</v>
+        <v>-4.584398</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.151881</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-124.390127158223</v>
+        <v>-127.123954381064</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-108.6420488115366</v>
+        <v>-109.6156159042659</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-57.12904034083568</v>
@@ -6101,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.138</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.138</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -25919,7 +25919,11 @@
           <t>Repayment of bank indebtedness (Note 19)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -27173,7 +27177,11 @@
           <t>Repayment of bank indebtedness (note 17)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -35327,7 +35335,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -40959,7 +40967,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -41688,7 +41696,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLN.xlsx
+++ b/output/pdf_financials_xlsx/BLN.xlsx
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.001846</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.007772</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.005143</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.038019</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.166098</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.295838</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.564816</v>
@@ -2256,22 +2256,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.734726</v>
+        <v>0.736572</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2.301168</v>
+        <v>2.30894</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.687613</v>
+        <v>0.692756</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.51961</v>
+        <v>1.557629</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.72302</v>
+        <v>2.889118</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>4.242421</v>
+        <v>4.538259</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>10.405669</v>
@@ -2578,22 +2578,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.268595</v>
+        <v>0.266749</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.417325</v>
+        <v>0.409553</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.408694</v>
+        <v>0.403551</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.56266</v>
+        <v>0.524641</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.296158</v>
+        <v>0.13006</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.963578</v>
+        <v>0.66774</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.704712</v>
@@ -3340,40 +3340,40 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.438549</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.769277</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.730453</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.179222</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.488292</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>2.281092</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>3.635092</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>3.453992</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>8.632999999999999</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>10.852</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>10.453</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>10.642</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>0</v>
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.227705</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.540315</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.583444</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.511705</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.972438</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.756159</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>3.732261</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>6.166</v>
@@ -3551,13 +3551,13 @@
         <v>16.139455</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>10.852</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>10.453</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>22.955</v>
+        <v>33.597</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>23.642</v>
@@ -3637,10 +3637,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.784</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -3683,10 +3683,10 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.784</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -3867,19 +3867,19 @@
         <v>0.899936</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.8215249999999999</v>
+        <v>0.324525</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1.148545</v>
+        <v>0.364545</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>22.837</v>
+        <v>11.985</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>31.208</v>
+        <v>20.755</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>10.924</v>
+        <v>0.282</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>5.713</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.01604173262773833</v>
+        <v>0.02353491036832663</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.02168043851754888</v>
+        <v>0.03237066732117047</v>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0.05</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0.05</v>
@@ -13773,7 +13773,11 @@
           <t>Lease liabilities (Note 20) 879</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -15950,7 +15954,11 @@
           <t>Lease liabilities (note 18)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -33795,7 +33803,11 @@
           <t>Increase in long term debt</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E342" s="5" t="n">
         <v>0.19</v>
       </c>
